--- a/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Copy Number Variation/GDC_CNV_DM.xlsx
+++ b/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Copy Number Variation/GDC_CNV_DM.xlsx
@@ -1,26 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjohnson/Projects/SDD-Dataset/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/Copy Number Variation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2607B00-1AF0-2342-8979-B83BA81FF8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C54EB73-1D6F-B240-97B3-6346FDDA092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12380" yWindow="8000" windowWidth="27240" windowHeight="16440"/>
+    <workbookView xWindow="860" yWindow="1660" windowWidth="27240" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GDC_CNV_DM" sheetId="1" r:id="rId1"/>
+    <sheet name="InfoSheet" sheetId="2" r:id="rId1"/>
+    <sheet name="Prefixes" sheetId="3" r:id="rId2"/>
+    <sheet name="Mapping Process" sheetId="4" r:id="rId3"/>
+    <sheet name="Timeline" sheetId="5" r:id="rId4"/>
+    <sheet name="New Concepts" sheetId="6" r:id="rId5"/>
+    <sheet name="Codebook" sheetId="7" r:id="rId6"/>
+    <sheet name="Dictionary Mapping" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
   <si>
     <t>Column</t>
   </si>
@@ -76,9 +82,6 @@
     <t>Sample</t>
   </si>
   <si>
-    <t>sio:Identifier</t>
-  </si>
-  <si>
     <t>??sample</t>
   </si>
   <si>
@@ -91,9 +94,6 @@
     <t>Start</t>
   </si>
   <si>
-    <t>sio:Coordinate</t>
-  </si>
-  <si>
     <t>??chromosome_start_position</t>
   </si>
   <si>
@@ -106,18 +106,12 @@
     <t>Num_Probes</t>
   </si>
   <si>
-    <t>sio:Count</t>
-  </si>
-  <si>
     <t>??probe</t>
   </si>
   <si>
     <t>Segment_Mean</t>
   </si>
   <si>
-    <t>sio:Mean</t>
-  </si>
-  <si>
     <t>??segment</t>
   </si>
   <si>
@@ -136,21 +130,12 @@
     <t>??subject</t>
   </si>
   <si>
-    <t>sio:Human</t>
-  </si>
-  <si>
-    <t>sio:SubjectRole</t>
-  </si>
-  <si>
     <t>??study</t>
   </si>
   <si>
     <t>hasco:Study</t>
   </si>
   <si>
-    <t>sio:Sample</t>
-  </si>
-  <si>
     <t>ncit:C43523</t>
   </si>
   <si>
@@ -158,13 +143,64 @@
   </si>
   <si>
     <t>go:0051303</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>sio</t>
+  </si>
+  <si>
+    <t>http://semanticscience.org/resource/</t>
+  </si>
+  <si>
+    <t>ncit</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#</t>
+  </si>
+  <si>
+    <t>hasco</t>
+  </si>
+  <si>
+    <t>http://hadatac.org/ont/hasco/</t>
+  </si>
+  <si>
+    <t>sio:SIO_000115</t>
+  </si>
+  <si>
+    <t>sio:SIO_000071</t>
+  </si>
+  <si>
+    <t>sio:SIO_000794</t>
+  </si>
+  <si>
+    <t>sio:SIO_001109</t>
+  </si>
+  <si>
+    <t>sio:SIO_000485</t>
+  </si>
+  <si>
+    <t>sio:SIO_000883</t>
+  </si>
+  <si>
+    <t>sio:SIO_001050</t>
+  </si>
+  <si>
+    <t>go</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/GO_</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -299,6 +335,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -481,7 +531,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -596,8 +646,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -640,11 +705,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -678,6 +747,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -997,9 +1067,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F542CE-4809-4748-AEF9-80D2E0C46E25}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E918A5-5D26-A944-B2C9-2EC5BCE5A551}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{4277048B-B918-E941-B595-4D5706C71F80}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{BC23A075-E0EF-FC42-AE2B-5F1D65C53AFD}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{7FFE1B4C-AFDC-284A-8F04-1C17A8F07B8B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{085D4A2A-7660-1A40-B8B6-06D9C5C0E8D1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DAA1AE-02E9-EA4C-BDF1-1EEF363958C3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA018B6E-4D47-5F4E-ACA0-57FB988FE223}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0575CBB0-3D43-194B-B4BD-3B5264CD1963}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1059,156 +1235,157 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
         <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>